--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.68596363427989</v>
+        <v>6.611469090570483</v>
       </c>
       <c r="D2" t="n">
-        <v>41.34578014098307</v>
+        <v>6.718689272909748</v>
       </c>
       <c r="E2" t="n">
-        <v>3.497078000512746</v>
+        <v>0.5682751750833213</v>
       </c>
       <c r="F2" t="n">
-        <v>16.39911729385767</v>
+        <v>2.664856560251872</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.75835299806064</v>
+        <v>7.110732362184855</v>
       </c>
       <c r="D3" t="n">
-        <v>11.92686044187656</v>
+        <v>1.938114821804942</v>
       </c>
       <c r="E3" t="n">
-        <v>3.497078000512746</v>
+        <v>0.5682751750833213</v>
       </c>
       <c r="F3" t="n">
-        <v>16.39911729385767</v>
+        <v>2.664856560251872</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.14699139253472</v>
+        <v>7.986386101286893</v>
       </c>
       <c r="D4" t="n">
-        <v>50.32355501570272</v>
+        <v>8.177577690051693</v>
       </c>
       <c r="E4" t="n">
-        <v>3.497078000512746</v>
+        <v>0.5682751750833213</v>
       </c>
       <c r="F4" t="n">
-        <v>16.39911729385767</v>
+        <v>2.664856560251872</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
